--- a/Analysed/Gemini/Analysis_Summary_Depth_without_vernier_pro.xlsx
+++ b/Analysed/Gemini/Analysis_Summary_Depth_without_vernier_pro.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.1338 ± 2.3635</t>
+          <t>8.0596 ± 2.5967</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.3270 ± 3.0770</t>
+          <t>8.9477 ± 2.9347</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.8916 ± 0.0378</t>
+          <t>0.4891 ± 0.3418</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,38 +521,114 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V1_5 divisions_per_second</t>
+          <t>V2_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
-        <v>7.462533333333331</v>
+        <v>8.613412698412699</v>
       </c>
       <c r="D2" t="n">
-        <v>8.151229191559597</v>
+        <v>9.249851092752532</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V2_10 divisions_per_second</t>
+          <t>V3_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>81</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.253086419753086</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.736952941093936</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2375</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>V4_1.7 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>57</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8.797192982456142</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.678490530416838</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1607142857142857</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V5_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>48</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.42625</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10.36665688638338</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5531914893617021</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V6_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.462533333333331</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.151229191559597</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8648648648648649</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V7_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>50</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C7" t="n">
         <v>10.805</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D7" t="n">
         <v>12.50280168602222</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E7" t="n">
         <v>0.9183673469387755</v>
       </c>
     </row>
